--- a/data/trans_orig/Q5415-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2007</t>
+          <t>Población según si es capaz de salir a caminar en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50544</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -846,47 +846,47 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>37038</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>36199</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49835</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37807</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66348</t>
+          <t>65042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61180</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92907</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>327880</t>
+          <t>328224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>348291</t>
+          <t>348465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>492242</t>
+          <t>491319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>524094</t>
+          <t>524760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>828124</t>
+          <t>829147</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>867651</t>
+          <t>866140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7253</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7180</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79634</t>
+          <t>79715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87160</t>
+          <t>87136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>50236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60208</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1465,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>141140</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>133096</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>145460</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>96,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>141140</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>133480</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>146183</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>62676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53037</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69914</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>67379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>452714</t>
+          <t>452426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474734</t>
+          <t>474765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>573141</t>
+          <t>573959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>609438</t>
+          <t>608800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1035031</t>
+          <t>1036994</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1077761</t>
+          <t>1078503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2012</t>
+          <t>Población según si es capaz de salir a caminar en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50978</t>
+          <t>49930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82161</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>68214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>107693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40536</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76047</t>
+          <t>73941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115703</t>
+          <t>112968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>350092</t>
+          <t>348001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378301</t>
+          <t>378112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>484422</t>
+          <t>482581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>524427</t>
+          <t>524269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>844659</t>
+          <t>844317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>895927</t>
+          <t>894712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103549</t>
+          <t>103182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114772</t>
+          <t>114702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68669</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80165</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178453</t>
+          <t>177131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193248</t>
+          <t>193108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46786</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85604</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71722</t>
+          <t>71956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112369</t>
+          <t>110960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>57459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90335</t>
+          <t>87424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131091</t>
+          <t>130979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>483320</t>
+          <t>483955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514973</t>
+          <t>514056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>576728</t>
+          <t>577056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>620732</t>
+          <t>619762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1072220</t>
+          <t>1072618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1127190</t>
+          <t>1128924</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2016</t>
+          <t>Población según si es capaz de salir a caminar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47028</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64216</t>
+          <t>62652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58917</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>93407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81325</t>
+          <t>80312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124057</t>
+          <t>122688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>325236</t>
+          <t>325367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>425640</t>
+          <t>425921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>467112</t>
+          <t>467145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>736722</t>
+          <t>735821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>784056</t>
+          <t>783889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>24667</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180891</t>
+          <t>180167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190036</t>
+          <t>189835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159096</t>
+          <t>159400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177639</t>
+          <t>177411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344084</t>
+          <t>344036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>365681</t>
+          <t>365591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62327</t>
+          <t>61101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73226</t>
+          <t>73594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44332</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77207</t>
+          <t>78150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71247</t>
+          <t>69229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109838</t>
+          <t>106723</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95717</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138455</t>
+          <t>139912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527120</t>
+          <t>528951</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>552353</t>
+          <t>552271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>620690</t>
+          <t>624406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668295</t>
+          <t>669339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1161881</t>
+          <t>1163020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1213229</t>
+          <t>1213920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2023</t>
+          <t>Población según si es capaz de salir a caminar en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72047</t>
+          <t>73986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64498</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89345</t>
+          <t>88824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82433</t>
+          <t>82059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>108086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109852</t>
+          <t>108753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139597</t>
+          <t>137390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>214827</t>
+          <t>215470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234328</t>
+          <t>234293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>328489</t>
+          <t>327741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>358501</t>
+          <t>357944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>551124</t>
+          <t>551376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>586200</t>
+          <t>586977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43254</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248795</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261938</t>
+          <t>262512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411662</t>
+          <t>410460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449061</t>
+          <t>448945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>670277</t>
+          <t>671047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>712324</t>
+          <t>712522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>94532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>102770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61822</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68494</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159528</t>
+          <t>159876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169967</t>
+          <t>170091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>28045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>36157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91031</t>
+          <t>90967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>57588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107392</t>
+          <t>109843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58027</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150091</t>
+          <t>149208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103625</t>
+          <t>101064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188456</t>
+          <t>189860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>569428</t>
+          <t>568288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>593759</t>
+          <t>593752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>790253</t>
+          <t>791254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933657</t>
+          <t>930367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1383124</t>
+          <t>1379692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1512484</t>
+          <t>1512720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5415-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25797</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>36913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>64710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>61856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92514</t>
+          <t>95540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>328224</t>
+          <t>326396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>348465</t>
+          <t>348235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491319</t>
+          <t>490676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>829147</t>
+          <t>826704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>866140</t>
+          <t>866681</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79715</t>
+          <t>79507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>87127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50236</t>
+          <t>50730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133096</t>
+          <t>133541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145460</t>
+          <t>145995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62676</t>
+          <t>63424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52381</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>42056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>67625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>102420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>452426</t>
+          <t>451397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474765</t>
+          <t>473541</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>573959</t>
+          <t>571277</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>608800</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1036994</t>
+          <t>1033966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078503</t>
+          <t>1076477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34436</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80012</t>
+          <t>81810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68214</t>
+          <t>68861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107693</t>
+          <t>107128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>81863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73941</t>
+          <t>73633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112968</t>
+          <t>113377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>348001</t>
+          <t>350983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>377752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>482581</t>
+          <t>484193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>524269</t>
+          <t>525449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>844317</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>894712</t>
+          <t>897449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103182</t>
+          <t>103510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69567</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80676</t>
+          <t>80888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177131</t>
+          <t>177715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193108</t>
+          <t>193480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88352</t>
+          <t>84459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71956</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110960</t>
+          <t>111612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57459</t>
+          <t>55093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90574</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87424</t>
+          <t>87695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130979</t>
+          <t>129078</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>483955</t>
+          <t>483579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514056</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>577056</t>
+          <t>577932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619762</t>
+          <t>621738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1072618</t>
+          <t>1071278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1128924</t>
+          <t>1126825</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>47696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62652</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58413</t>
+          <t>58578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>93704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80312</t>
+          <t>80145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>119883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>303019</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>325367</t>
+          <t>325982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>425921</t>
+          <t>422962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>467145</t>
+          <t>465759</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>735821</t>
+          <t>737945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>783889</t>
+          <t>785416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180167</t>
+          <t>180202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189835</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159400</t>
+          <t>160947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177411</t>
+          <t>178206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344036</t>
+          <t>345262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>365591</t>
+          <t>365054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>34101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61101</t>
+          <t>61593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>73401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57100</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>42658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>76540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69229</t>
+          <t>70666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106723</t>
+          <t>107793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98946</t>
+          <t>96501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139912</t>
+          <t>139115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>528951</t>
+          <t>527723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>552271</t>
+          <t>551754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>624406</t>
+          <t>623877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>669339</t>
+          <t>668702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1163020</t>
+          <t>1161794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1213920</t>
+          <t>1214350</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22079</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>68089</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52715</t>
+          <t>56287</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>80724</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76603</t>
+          <t>83690</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88824</t>
+          <t>97387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>30684</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>40490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94367</t>
+          <t>101663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82059</t>
+          <t>87508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108086</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>123506</t>
+          <t>132347</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108753</t>
+          <t>116288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137390</t>
+          <t>148909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>225302</t>
+          <t>243810</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215470</t>
+          <t>232800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234293</t>
+          <t>253271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>344001</t>
+          <t>368434</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>327741</t>
+          <t>353464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>357944</t>
+          <t>385272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>569302</t>
+          <t>612243</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>551376</t>
+          <t>590720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>586977</t>
+          <t>629272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500168</t>
+          <t>538185</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500168</t>
+          <t>538185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500168</t>
+          <t>538185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769411</t>
+          <t>828280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769411</t>
+          <t>828280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769411</t>
+          <t>828280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,27 +7349,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>27937</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>42033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>256732</t>
+          <t>286176</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>249488</t>
+          <t>278663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262512</t>
+          <t>292126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>433055</t>
+          <t>250872</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>410460</t>
+          <t>243281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>448945</t>
+          <t>257316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>689787</t>
+          <t>537048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671047</t>
+          <t>526243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>712522</t>
+          <t>546655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455306</t>
+          <t>277180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455306</t>
+          <t>277180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455306</t>
+          <t>277180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728563</t>
+          <t>581005</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728563</t>
+          <t>581005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728563</t>
+          <t>581005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99942</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94532</t>
+          <t>106482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>116330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62015</t>
+          <t>71879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>79310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>189350</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159876</t>
+          <t>182667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170091</t>
+          <t>193966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69079</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>64727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90967</t>
+          <t>89853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>97757</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57588</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109843</t>
+          <t>115538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45269</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>37801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>126717</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58505</t>
+          <t>112292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149208</t>
+          <t>141863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>160109</t>
+          <t>174622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101064</t>
+          <t>155800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189860</t>
+          <t>195228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>581976</t>
+          <t>643031</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>568288</t>
+          <t>629650</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>593752</t>
+          <t>655111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>842879</t>
+          <t>695610</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>791254</t>
+          <t>674830</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>930367</t>
+          <t>711922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1424855</t>
+          <t>1338642</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1379692</t>
+          <t>1311741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1512720</t>
+          <t>1361121</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1026798</t>
+          <t>898220</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1026798</t>
+          <t>898220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1026798</t>
+          <t>898220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674285</t>
+          <t>1611022</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674285</t>
+          <t>1611022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674285</t>
+          <t>1611022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
